--- a/docs/AlloQuant_master_CSV_data_dictionary_v7r3.xlsx
+++ b/docs/AlloQuant_master_CSV_data_dictionary_v7r3.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Activation-loop C-terminal packing: CTin if the pre-APE window (ape-6 down to ape-9, floored at f+2) comes within 5.5 A (all-atom) of the HRD arginine (hrd+1), else CTout; N/A if the residues are not contiguous in the deposited numbering. The hrd+1 anchor follows Modi &amp; Dunbrack's APE9-Arg contact (v7r2 used hrd+6, which is an Arg in CSK but an Ala in SRC). The 5.5 A cutoff is AlloQuant's own sensitivity choice, deliberately looser than Kincore's 6.0 A.</t>
+          <t>Activation-loop C-terminal packing: CTin if the pre-APE window (ape-6 down to ape-9, floored at f+2) comes within 5.5 A (all-atom) of the HRD arginine (hrd+1), else CTout; N/A if the residues are not contiguous in the deposited numbering. The hrd+1 anchor follows Modi &amp; Dunbrack's APE9-Arg contact (v7r2 used hrd+6, which is an Arg in CSK but an Ala in SRC); only the anchor changed at v7r3, the window and the 5.5 A all-atom cutoff being inherited unchanged from v6r6. NOT COMPARABLE WITH KINCORE'S ActLoopCT LABEL: Kincore measures two named atoms of the single APE9 residue (CA to the Arg backbone O) at 6.0 A, whereas this is an all-atom minimum over four residues at 5.5 A. The 5.5 A cutoff is stricter than Kincore's 6.0 A; it is the four-residue window, not the cutoff, that makes this the more permissive criterion. Because the value is an all-atom minimum over whatever side chains occupy the window, it is also sequence-dependent across kinases.</t>
         </is>
       </c>
     </row>

--- a/docs/AlloQuant_master_CSV_data_dictionary_v7r3.xlsx
+++ b/docs/AlloQuant_master_CSV_data_dictionary_v7r3.xlsx
@@ -604,7 +604,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>- Distances in Angstrom (A), angles in degrees. Landmark indices are 0-based HMM-aligned positions; numbered landmarks (n99, v104, k105, e107, m118, m120, e121, i150, y156, d220) are labelled in CSK numbering and map to the equivalent target position via the HMM.</t>
+          <t>- Distances in Angstrom (A), angles in degrees. Landmark indices are 0-based HMM-aligned positions; numbered landmarks (n99, v104, k105, e107, m118, m120, e121, i150, y156, d220) are labelled in PKA numbering (the canonical reference kinase), and map to the equivalent target position via the HMM regardless of the residue type actually present.</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Min side-chain distance between the two shell methionines M118 and M120 (drives Shell_State).</t>
+          <t>Min side-chain distance between the two hydrophobic-shell positions M118 and M120 (PKA numbering; Ile79/Thr81 in CSK and SRC, Leu78/Phe80 in CDK1); drives Shell_State.</t>
         </is>
       </c>
     </row>

--- a/docs/AlloQuant_master_CSV_data_dictionary_v7r3.xlsx
+++ b/docs/AlloQuant_master_CSV_data_dictionary_v7r3.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Activation-loop C-terminal packing: CTin if the pre-APE window (ape-6 down to ape-9, floored at f+2) comes within 5.5 A (all-atom) of the HRD arginine (hrd+1), else CTout; N/A if the residues are not contiguous in the deposited numbering. The hrd+1 anchor follows Modi &amp; Dunbrack's APE9-Arg contact (v7r2 used hrd+6, which is an Arg in CSK but an Ala in SRC); only the anchor changed at v7r3, the window and the 5.5 A all-atom cutoff being inherited unchanged from v6r6. NOT COMPARABLE WITH KINCORE'S ActLoopCT LABEL: Kincore measures two named atoms of the single APE9 residue (CA to the Arg backbone O) at 6.0 A, whereas this is an all-atom minimum over four residues at 5.5 A. The 5.5 A cutoff is stricter than Kincore's 6.0 A; it is the four-residue window, not the cutoff, that makes this the more permissive criterion. Because the value is an all-atom minimum over whatever side chains occupy the window, it is also sequence-dependent across kinases.</t>
+          <t>Activation-loop C-terminal packing: CTin if the pre-APE window (ape-6 down to ape-9, floored at f+2) comes within 5.5 A (all-atom) of the HRD arginine (hrd+1), else CTout; N/A if the residues are not contiguous in the deposited numbering. The hrd+1 anchor follows Modi &amp; Dunbrack's APE9-Arg contact (v7r2 used hrd+6, which is an Arg in CSK but an Ala in SRC); only the anchor changed at v7r3, the window and the 5.5 A all-atom cutoff being inherited unchanged from v6r6. NOT INTERCHANGEABLE WITH KINCORE'S ActLoopCT LABEL: both ask the same structural question of the same anchor, and this window contains Kincore's APE9, but the criteria differ. Kincore evaluates two named atoms of the single APE9 residue (CA to the Arg backbone O) at 6.0 A, whereas this is an all-atom minimum over four residues at 5.5 A. Agreement between the two is therefore agreement of criteria rather than reproduction of a shared measurement, and a concordance percentage should not be quoted. The 5.5 A cutoff is stricter than Kincore's 6.0 A; it is the four-residue window, not the cutoff, that makes this the more permissive criterion. Because the value is an all-atom minimum over whatever side chains occupy the window, it is also sequence-dependent across kinases.</t>
         </is>
       </c>
     </row>
